--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/SOUTH_CAROLINA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/SOUTH_CAROLINA_2021.xlsx
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C244">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C254">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C689">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C690">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C735">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C736">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C743">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C833">
